--- a/data/trans_dic/IP16A06-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A06-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes</t>
+          <t>Menores que consumiero  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,81</t>
+          <t>0,0; 15,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,63</t>
+          <t>0,0; 16,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,92</t>
+          <t>0,0; 15,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,21</t>
+          <t>0,0; 11,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,14</t>
+          <t>0,0; 9,06</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,25</t>
+          <t>0,0; 18,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,65</t>
+          <t>0,0; 8,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,35</t>
+          <t>0,0; 29,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,82</t>
+          <t>0,0; 11,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,26</t>
+          <t>0,0; 11,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,6</t>
+          <t>0,0; 5,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,16</t>
+          <t>0,0; 11,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,54</t>
+          <t>0,0; 5,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,0</t>
+          <t>0,0; 10,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,16</t>
+          <t>0,78; 7,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,56</t>
+          <t>0,0; 3,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,44</t>
+          <t>0,0; 9,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,49</t>
+          <t>0,0; 10,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,94</t>
+          <t>0,0; 18,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,06</t>
+          <t>0,0; 10,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,6</t>
+          <t>0,0; 12,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,77</t>
+          <t>0,0; 11,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,52</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,01</t>
+          <t>0,79; 7,3</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,29</t>
+          <t>0,0; 27,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,68</t>
+          <t>0,0; 22,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,16</t>
+          <t>0,0; 17,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,87</t>
+          <t>0,54; 5,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,21</t>
+          <t>0,45; 4,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,12</t>
+          <t>0,51; 5,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,64</t>
+          <t>0,39; 3,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,97</t>
+          <t>0,41; 3,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,87</t>
+          <t>0,82; 3,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,1</t>
+          <t>0,73; 3,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,44</t>
+          <t>0,3; 2,27</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1520</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4103</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4218</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3344</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5715</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3628</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3220</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3291</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3266</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3823</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1389</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2114</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1366</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4468</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3065</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4580</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3880</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4342</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>597; 6036</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4834</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2985</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1263</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1767</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3651</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3922</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4308</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3421</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3706</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4744</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3850</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>518; 4821</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1465</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3265</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3206</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4666</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2947</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2661</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>4704</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>5614</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>597; 5745</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>806; 7489</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3706</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>696; 6801</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>691; 6020</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>582; 5020</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2004; 9530</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2625; 11356</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>886; 6736</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A06-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A06-Clase-trans_dic.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,31</t>
+          <t>0,0; 15,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,9</t>
+          <t>0,0; 14,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,9</t>
+          <t>0,0; 13,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,04</t>
+          <t>0,0; 10,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,06</t>
+          <t>0,0; 8,3</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,03</t>
+          <t>0,0; 18,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,83</t>
+          <t>0,0; 7,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,39</t>
+          <t>0,0; 24,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,56</t>
+          <t>0,0; 10,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,86</t>
+          <t>0,0; 11,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,07</t>
+          <t>0,0; 6,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,32 +1023,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,81</t>
+          <t>0,0; 10,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,33</t>
+          <t>0,0; 5,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,1</t>
+          <t>0,0; 6,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,89</t>
+          <t>0,79; 7,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 3,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
     </row>
@@ -1123,42 +1123,42 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,71</t>
+          <t>0,0; 8,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,96</t>
+          <t>0,0; 10,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,03</t>
+          <t>0,0; 16,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,17</t>
+          <t>0,0; 7,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,25</t>
+          <t>0,0; 10,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,1</t>
+          <t>0,0; 9,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>0,0; 6,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 7,3</t>
+          <t>0,78; 6,55</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,68</t>
+          <t>0,0; 39,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,15</t>
+          <t>0,0; 19,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,76</t>
+          <t>0,0; 19,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,24</t>
+          <t>0,55; 5,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,2</t>
+          <t>0,44; 3,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,03</t>
+          <t>0,48; 4,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,36</t>
+          <t>0,36; 3,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,58</t>
+          <t>0,42; 3,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,89</t>
+          <t>0,83; 3,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,18</t>
+          <t>0,74; 3,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,27</t>
+          <t>0,38; 2,16</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4103</t>
+          <t>0; 4041</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4218</t>
+          <t>0; 3574</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3344</t>
+          <t>0; 2906</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5715</t>
+          <t>0; 5345</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3628</t>
+          <t>0; 3323</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3220</t>
+          <t>0; 3309</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3291</t>
+          <t>0; 2619</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3266</t>
+          <t>0; 2713</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3823</t>
+          <t>0; 3325</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4468</t>
+          <t>0; 4282</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3065</t>
+          <t>0; 3810</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2143,32 +2143,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4580</t>
+          <t>0; 4133</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3880</t>
+          <t>0; 3731</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4342</t>
+          <t>0; 3000</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>597; 6036</t>
+          <t>600; 6111</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4834</t>
+          <t>0; 4722</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 2985</t>
+          <t>0; 3377</t>
         </is>
       </c>
     </row>
@@ -2296,42 +2296,42 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3651</t>
+          <t>0; 3240</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3922</t>
+          <t>0; 3607</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4308</t>
+          <t>0; 3921</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3421</t>
+          <t>0; 2579</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3706</t>
+          <t>0; 3210</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4744</t>
+          <t>0; 4051</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3850</t>
+          <t>0; 4518</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>518; 4821</t>
+          <t>516; 4324</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3265</t>
+          <t>0; 4658</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3206</t>
+          <t>0; 2817</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4666</t>
+          <t>0; 5017</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>597; 5745</t>
+          <t>598; 5915</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>806; 7489</t>
+          <t>793; 6874</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3706</t>
+          <t>0; 3875</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>696; 6801</t>
+          <t>649; 6106</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>691; 6020</t>
+          <t>649; 6070</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>582; 5020</t>
+          <t>583; 4945</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2004; 9530</t>
+          <t>2043; 9548</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2625; 11356</t>
+          <t>2630; 10942</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>886; 6736</t>
+          <t>1114; 6398</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A06-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A06-Clase-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -630,27 +630,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2,89%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,98%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,08</t>
+          <t>0,0; 14,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 12,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,32</t>
+          <t>0,0; 14,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,33</t>
+          <t>0,0; 10,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,3</t>
+          <t>0,0; 8,14</t>
         </is>
       </c>
     </row>
@@ -735,22 +735,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 19,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,02</t>
+          <t>0,0; 9,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -845,22 +845,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>5,88%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 29,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,06</t>
+          <t>0,0; 9,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>3,69%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,36</t>
+          <t>0,0; 11,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,3</t>
+          <t>0,0; 4,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,66</t>
+          <t>0,0; 12,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,13</t>
+          <t>0,0; 5,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 7,99</t>
+          <t>0,78; 7,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,54</t>
+          <t>0,0; 3,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,39</t>
+          <t>0,0; 3,16</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,41%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,74%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>3,19%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 16,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,62</t>
+          <t>0,0; 9,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,08</t>
+          <t>0,0; 9,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,67</t>
+          <t>0,0; 8,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,61</t>
+          <t>0,0; 9,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,48</t>
+          <t>0,0; 10,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,34</t>
+          <t>0,0; 5,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,55</t>
+          <t>0,77; 7,01</t>
         </is>
       </c>
     </row>
@@ -1180,22 +1180,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>6,94%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,49</t>
+          <t>0,0; 18,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,46</t>
+          <t>0,0; 36,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,1</t>
+          <t>0,0; 18,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,86%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1,65%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>0,73%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,39</t>
+          <t>0,53; 5,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,86</t>
+          <t>0,36; 3,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>0,42; 3,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,51</t>
+          <t>0,54; 4,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,39</t>
+          <t>0,38; 4,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,52</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,9</t>
+          <t>0,82; 3,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,06</t>
+          <t>0,74; 3,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,16</t>
+          <t>0,39; 2,44</t>
         </is>
       </c>
     </row>
@@ -1432,20 +1432,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1591,27 +1591,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>798</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4041</t>
+          <t>0; 3652</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2717</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3574</t>
+          <t>0; 3970</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2906</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5345</t>
+          <t>0; 5285</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3323</t>
+          <t>0; 3258</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>642</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3438</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3309</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2619</t>
+          <t>0; 3599</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1859,22 +1859,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1912,22 +1912,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>654</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2713</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3260</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3325</t>
+          <t>0; 3247</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1389</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>675</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4282</t>
+          <t>0; 4328</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3810</t>
+          <t>0; 3301</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3008</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4133</t>
+          <t>0; 4619</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 3731</t>
+          <t>0; 3388</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3000</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>600; 6111</t>
+          <t>596; 5479</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4722</t>
+          <t>0; 4738</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3377</t>
+          <t>0; 3148</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1141</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1293</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4049</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3240</t>
+          <t>0; 3046</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3607</t>
+          <t>0; 2905</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3921</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2579</t>
+          <t>0; 3175</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3210</t>
+          <t>0; 3396</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4051</t>
+          <t>0; 4606</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4518</t>
+          <t>0; 3930</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>516; 4324</t>
+          <t>506; 4628</t>
         </is>
       </c>
     </row>
@@ -2406,22 +2406,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>818</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4658</t>
+          <t>0; 2703</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2817</t>
+          <t>0; 4280</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 5017</t>
+          <t>0; 4770</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>2661</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>2043</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>2947</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>1141</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2661</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2667</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>1859</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>598; 5915</t>
+          <t>723; 6925</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>793; 6874</t>
+          <t>652; 6515</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3875</t>
+          <t>586; 5578</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>649; 6106</t>
+          <t>594; 5341</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>649; 6070</t>
+          <t>685; 7501</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>583; 4945</t>
+          <t>0; 3731</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2043; 9548</t>
+          <t>2003; 9474</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2630; 10942</t>
+          <t>2661; 11082</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1114; 6398</t>
+          <t>1144; 7233</t>
         </is>
       </c>
     </row>
